--- a/knot-excel/tests/test_multi_block.xlsx
+++ b/knot-excel/tests/test_multi_block.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MultiBlock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiBlock" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,72 +484,72 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>利润</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1月</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3000</v>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>利润</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="C10" t="n">
-        <v>3500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="C11" t="n">
-        <v>4200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>11000</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>3100</v>
       </c>
     </row>
